--- a/stories/arbres/ATOM-VIV.PLA.001-11.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-11.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maxime est au jardin avec papa. Une petite tomate a soif. Papa dit : la plante a besoin d'eau. Elle a besoin de lumière. Maxime prend l'arrosoir. Papa, l'adulte, tient aussi l'anse. Ils versent un peu d'eau. La terre devient sombre. La lumière du soleil arrive. Papa dit : on arrose avec un adulte.</t>
+          <t>Maxime est au jardin avec papa. Une petite tomate a soif. La plante a besoin d'eau. Elle a besoin de lumière. Maxime prend l'arrosoir. Papa, l'adulte, tient aussi l'anse. Ils versent un peu d'eau. La terre devient sombre. La lumière du soleil arrive. On arrose avec un adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Maxime est au jardin avec papa. Une petite tomate a soif.
+papa|La plante a besoin d'eau. Elle a besoin de lumière.
+narrateur|Maxime prend l'arrosoir. Papa, l'adulte, tient aussi l'anse. Ils versent un peu d'eau. La terre devient sombre. La lumière du soleil arrive.
+papa|On arrose avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1489,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|La tomate a soif. Que fait Maxime avec papa ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1662,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Maxime a versé l'eau. La lumière est là. Papa, l'adulte, était avec lui.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1825,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maxime range l'arrosoir. La tomate sent le soleil.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1992,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2032,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.PLA.001-11.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-11.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 papa|On arrose avec un adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1496,6 +1502,7 @@
           <t>narrateur|La tomate a soif. Que fait Maxime avec papa ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1667,6 +1674,7 @@
           <t>narrateur|Maxime a versé l'eau. La lumière est là. Papa, l'adulte, était avec lui.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1830,6 +1838,7 @@
           <t>narrateur|Maxime range l'arrosoir. La tomate sent le soleil.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1997,6 +2006,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2015,7 +2025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2039,6 +2049,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2240,6 +2264,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.PLA.001-11.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-11.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Maxime arrose la tomate</t>
+          <t>La tomate rouge de Nina</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nina veut goûter la tomate cerise rouge avec papa. Elle croque d'abord une verte, trop dure. Ils arrosent. Ils goûtent la rouge, tiède.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maxime est au jardin avec papa. Une petite tomate a soif. La plante a besoin d'eau. Elle a besoin de lumière. Maxime prend l'arrosoir. Papa, l'adulte, tient aussi l'anse. Ils versent un peu d'eau. La terre devient sombre. La lumière du soleil arrive. On arrose avec un adulte.</t>
+          <t>Des tomates cerises pendent, toutes petites. Une est verte, bien ronde. Une autre est rouge, déjà chaude. L'herbe gratte un peu les chevilles. Un arrosoir bleu attend près du pied. La terre du pot est un peu pâle. Tu les vois, Nina ? Oui, papa. Je veux goûter la rouge. Avec moi ? Oui, avec toi. En ce moment, Nina tend la main. Ses doigts trouvent d'abord la verte. Elle la détache tout doux. Celle-là, tu es sûre ? Elle est ronde. Nina croque un tout petit peu. Elle est dure, papa. Elle n'est pas prête. La rouge a eu plus de soleil. Nina pose la verte dans la main de papa. Les feuilles du pied sont un peu molles. La terre a soif, tu vois ? La plante a besoin d'eau. Elle a besoin de lumière. On arrose, alors ? Oui, avec moi. Nina prend l'arrosoir bleu. Papa tient aussi l'anse. Ils versent un peu d'eau au pied. La terre devient sombre. Elle boit. Oui. Une abeille passe tout près, puis s'en va. Nina essuie une goutte sur une feuille. La rouge est encore là. Elle attend un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maxime est au jardin avec papa. Une petite tomate a soif. Papa dit : la plante a besoin d'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;. Elle a besoin de lumière. Maxime prend l'arrosoir. Papa, l'adulte, tient aussi l'anse. Ils versent un peu d'eau. La terre devient sombre. La lumière du soleil arrive. Papa dit : on arrose avec un adulte.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Des tomates cerises pendent, toutes petites. Une est verte, bien ronde. Une autre est rouge, déjà chaude. L'herbe gratte un peu les chevilles. Un arrosoir bleu attend près du pied. La terre du pot est un peu pâle. Tu les vois, Nina ? Oui, papa. Je veux goûter la rouge. Avec moi ? Oui, avec toi. En ce moment, Nina tend la main. Ses doigts trouvent d'abord la verte. Elle la détache tout doux. Celle-là, tu es sûre ? Elle est ronde. Nina croque un tout petit peu. Elle est dure, papa. Elle n'est pas prête. La rouge a eu plus de soleil. Nina pose la verte dans la main de papa. Les feuilles du pied sont un peu molles. La terre a soif, tu vois ? La plante a besoin d'eau. Elle a besoin de lumière. On arrose, alors ? Oui, avec moi. Nina prend l'arrosoir bleu. Papa tient aussi l'anse. Ils versent un peu d'eau au pied. La terre devient sombre. Elle boit. Oui. Une abeille passe tout près, puis s'en va. Nina essuie une goutte sur une feuille. La rouge est encore là. Elle attend un peu.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,13 +1324,45 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Maxime est au jardin avec papa. Une petite tomate a soif.
-papa|La plante a besoin d'eau. Elle a besoin de lumière.
-narrateur|Maxime prend l'arrosoir. Papa, l'adulte, tient aussi l'anse. Ils versent un peu d'eau. La terre devient sombre. La lumière du soleil arrive.
-papa|On arrose avec un adulte.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Des tomates cerises pendent, toutes petites.
+narrateur|Une est verte, bien ronde.
+narrateur|Une autre est rouge, déjà chaude.
+narrateur|L'herbe gratte un peu les chevilles.
+narrateur|Un arrosoir bleu attend près du pied.
+narrateur|La terre du pot est un peu pâle.
+papa|Tu les vois, Nina ?
+enfant-f|Oui, papa.
+enfant-f|Je veux goûter la rouge.
+papa|Avec moi ?
+enfant-f|Oui, avec toi.
+narrateur|En ce moment, Nina tend la main.
+narrateur|Ses doigts trouvent d'abord la verte.
+narrateur|Elle la détache tout doux.
+papa|Celle-là, tu es sûre ?
+enfant-f|Elle est ronde.
+narrateur|Nina croque un tout petit peu.
+enfant-f|Elle est dure, papa.
+papa|Elle n'est pas prête.
+papa|La rouge a eu plus de soleil.
+narrateur|Nina pose la verte dans la main de papa.
+narrateur|Les feuilles du pied sont un peu molles.
+papa|La terre a soif, tu vois ?
+papa|La plante a besoin d'eau.
+papa|Elle a besoin de lumière.
+enfant-f|On arrose, alors ?
+papa|Oui, avec moi.
+narrateur|Nina prend l'arrosoir bleu.
+narrateur|Papa tient aussi l'anse.
+narrateur|Ils versent un peu d'eau au pied.
+narrateur|La terre devient sombre.
+enfant-f|Elle boit.
+papa|Oui.
+narrateur|Une abeille passe tout près, puis s'en va.
+narrateur|Nina essuie une goutte sur une feuille.
+enfant-f|La rouge est encore là.
+papa|Elle attend un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1343,12 +1387,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>La tomate a soif. Que fait Maxime avec papa ?</t>
+          <t>La tomate a soif. Que fait Nina avec papa ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;La tomate a soif. Que fait Maxime avec papa ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>La tomate a soif. Que fait Nina avec papa ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1363,7 +1407,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>arroser | de l'eau | eau</t>
+          <t>arroser | de l'eau | eau | lumière | avec papa</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1378,7 +1422,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Ils versent de l'eau. Que fait Maxime ?</t>
+          <t>Ils versent de l'eau. Que fait Nina ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1427,7 +1471,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1499,10 +1543,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|La tomate a soif. Que fait Maxime avec papa ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|La tomate a soif.
+narrateur|Que fait Nina avec papa ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1527,12 +1571,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Maxime a versé l'eau. La lumière est là. Papa, l'adulte, était avec lui.</t>
+          <t>Nina pose l'arrosoir dans l'herbe. L'herbe est un peu mouillée. La rouge, maintenant ? Oui. Papa penche une feuille. La tomate rouge est tiède. On la cueille ensemble ? Oui, papa. Nina la tient, et papa aide. La tomate se détache, toute ronde. Merci, Nina. Tu as arrosé, d'abord. Pour la plante. Pour qu'elle fasse encore des rouges. Nina souffle un peu sur la tomate. Un grain de terre tombe. Tu goûtes ? Avec toi.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maxime a versé l'&lt;emphasis level="moderate"&gt;eau&lt;/emphasis&gt;. La lumière est là. Papa, l'adulte, était avec lui.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina pose l'arrosoir dans l'herbe. L'herbe est un peu mouillée. La rouge, maintenant ? Oui. Papa penche une feuille. La tomate rouge est tiède. On la cueille ensemble ? Oui, papa. Nina la tient, et papa aide. La tomate se détache, toute ronde. Merci, Nina. Tu as arrosé, d'abord. Pour la plante. Pour qu'elle fasse encore des rouges. Nina souffle un peu sur la tomate. Un grain de terre tombe. Tu goûtes ? Avec toi.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1595,7 +1639,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1671,10 +1715,26 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Maxime a versé l'eau. La lumière est là. Papa, l'adulte, était avec lui.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nina pose l'arrosoir dans l'herbe.
+narrateur|L'herbe est un peu mouillée.
+papa|La rouge, maintenant ?
+enfant-f|Oui.
+narrateur|Papa penche une feuille.
+narrateur|La tomate rouge est tiède.
+papa|On la cueille ensemble ?
+enfant-f|Oui, papa.
+narrateur|Nina la tient, et papa aide.
+narrateur|La tomate se détache, toute ronde.
+papa|Merci, Nina.
+papa|Tu as arrosé, d'abord.
+enfant-f|Pour la plante.
+papa|Pour qu'elle fasse encore des rouges.
+narrateur|Nina souffle un peu sur la tomate.
+narrateur|Un grain de terre tombe.
+papa|Tu goûtes ?
+enfant-f|Avec toi.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1699,12 +1759,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maxime range l'arrosoir. La tomate sent le soleil.</t>
+          <t>Nina croque la rouge. Elle est sucrée. Et tiède. Papa croque l'autre moitié. Le jus sent le soleil. La verte, on la laisse ? Oui, elle va mûrir. Avec de l'eau et de la lumière. Nina essuie ses doigts sur l'herbe. L'arrosoir bleu reste près du pied. On range l'arrosoir ? Oui, papa. Nina pose l'arrosoir près du pied. Le bleu de l'arrosoir brille un peu. La verte va devenir rouge ? Avec de l'eau, et du soleil.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maxime range l'arrosoir. La tomate sent le soleil.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina croque la rouge. Elle est sucrée. Et tiède. Papa croque l'autre moitié. Le jus sent le soleil. La verte, on la laisse ? Oui, elle va mûrir. Avec de l'eau et de la lumière. Nina essuie ses doigts sur l'herbe. L'arrosoir bleu reste près du pied. On range l'arrosoir ? Oui, papa. Nina pose l'arrosoir près du pied. Le bleu de l'arrosoir brille un peu. La verte va devenir rouge ? Avec de l'eau, et du soleil.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1767,7 +1827,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1835,10 +1895,24 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maxime range l'arrosoir. La tomate sent le soleil.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Nina croque la rouge.
+enfant-f|Elle est sucrée.
+papa|Et tiède.
+narrateur|Papa croque l'autre moitié.
+narrateur|Le jus sent le soleil.
+enfant-f|La verte, on la laisse ?
+papa|Oui, elle va mûrir.
+papa|Avec de l'eau et de la lumière.
+narrateur|Nina essuie ses doigts sur l'herbe.
+narrateur|L'arrosoir bleu reste près du pied.
+papa|On range l'arrosoir ?
+enfant-f|Oui, papa.
+narrateur|Nina pose l'arrosoir près du pied.
+narrateur|Le bleu de l'arrosoir brille un peu.
+enfant-f|La verte va devenir rouge ?
+papa|Avec de l'eau, et du soleil.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1863,12 +1937,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La tomate rouge a goûté le soleil. On l'a goûtée aussi. Oui. Le pied tient dans la terre sombre. La verte attend encore un peu de jour.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La tomate rouge a goûté le soleil. On l'a goûtée aussi. Oui. Le pied tient dans la terre sombre. La verte attend encore un peu de jour.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1924,14 +1998,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2003,10 +2077,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|La tomate rouge a goûté le soleil.
+enfant-f|On l'a goûtée aussi.
+papa|Oui.
+narrateur|Le pied tient dans la terre sombre.
+narrateur|La verte attend encore un peu de jour.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2025,7 +2102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2063,6 +2140,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.PLA.001-11.xlsx
+++ b/stories/arbres/ATOM-VIV.PLA.001-11.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin</t>
+          <t>jardin, pied de tomate cerise</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Maxime, papa</t>
+          <t>Nina, papa</t>
         </is>
       </c>
     </row>
